--- a/EmployeeBillableData_6.xlsx
+++ b/EmployeeBillableData_6.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="98">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -42,6 +42,270 @@
   </si>
   <si>
     <t>Client</t>
+  </si>
+  <si>
+    <t>A-20066</t>
+  </si>
+  <si>
+    <t>Jhimly Kar Hazra</t>
+  </si>
+  <si>
+    <t>jhimly.hazra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>InternalRNDProducts</t>
+  </si>
+  <si>
+    <t>Business Development</t>
+  </si>
+  <si>
+    <t>Sangeeta Padhy</t>
+  </si>
+  <si>
+    <t>Bishnu Pada Rath</t>
+  </si>
+  <si>
+    <t>ApMoSys-HR</t>
+  </si>
+  <si>
+    <t>ApMoSys</t>
+  </si>
+  <si>
+    <t>A-23208</t>
+  </si>
+  <si>
+    <t>Puspak Kumar Patnaik</t>
+  </si>
+  <si>
+    <t>puspak.patnaik@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-23365</t>
+  </si>
+  <si>
+    <t>Manoj Kumar Sethi</t>
+  </si>
+  <si>
+    <t>manoj.sethi@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Bibhu Padhi</t>
+  </si>
+  <si>
+    <t>A-250260</t>
+  </si>
+  <si>
+    <t>Abhilash Daspattnaik</t>
+  </si>
+  <si>
+    <t>abhilash.daspattnaik@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250272</t>
+  </si>
+  <si>
+    <t>Ganesh Bhaskar Rasal</t>
+  </si>
+  <si>
+    <t>ganesh.rasal@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>internal_testing_may15</t>
+  </si>
+  <si>
+    <t>A-250291</t>
+  </si>
+  <si>
+    <t>Ajay Afre</t>
+  </si>
+  <si>
+    <t>ajay.afre@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260133</t>
+  </si>
+  <si>
+    <t>Arijit Pal</t>
+  </si>
+  <si>
+    <t>arijit.pal@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-24006</t>
+  </si>
+  <si>
+    <t>Manoj Kumar Ramchandran</t>
+  </si>
+  <si>
+    <t>manojkumar.r@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>ApMoSys-BD</t>
+  </si>
+  <si>
+    <t>A-22135</t>
+  </si>
+  <si>
+    <t>Bandana Bijayalaxmi</t>
+  </si>
+  <si>
+    <t>bandana.bijayalaxmi@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-240303</t>
+  </si>
+  <si>
+    <t>Arin Agarwal</t>
+  </si>
+  <si>
+    <t>arin.agarwal@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250106</t>
+  </si>
+  <si>
+    <t>Raj Patil</t>
+  </si>
+  <si>
+    <t>raj.patil@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250237</t>
+  </si>
+  <si>
+    <t>Asutosh Kumar Pathak</t>
+  </si>
+  <si>
+    <t>asutosh.pathak@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260330</t>
+  </si>
+  <si>
+    <t>Biswaranjan Mishra</t>
+  </si>
+  <si>
+    <t>biswaranjan.mishra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-23170</t>
+  </si>
+  <si>
+    <t>Alokesh Mishra</t>
+  </si>
+  <si>
+    <t>alokesh.mishra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-240252</t>
+  </si>
+  <si>
+    <t>Deepika Udeshi Sampat</t>
+  </si>
+  <si>
+    <t>deepika.udeshi@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-240381</t>
+  </si>
+  <si>
+    <t>Snehil S Kumar</t>
+  </si>
+  <si>
+    <t>snehil.kumar@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250044</t>
+  </si>
+  <si>
+    <t>Deepak Raj</t>
+  </si>
+  <si>
+    <t>deepak.raj@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250111</t>
+  </si>
+  <si>
+    <t>Nikhilesh Dubey</t>
+  </si>
+  <si>
+    <t>nikhilesh.dubey@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-23294</t>
+  </si>
+  <si>
+    <t>Saurav Kumar Bakshi</t>
+  </si>
+  <si>
+    <t>saurav.bakshi@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-22358</t>
+  </si>
+  <si>
+    <t>Shakti Prasad Sahu</t>
+  </si>
+  <si>
+    <t>shakti.sahu@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-1979</t>
+  </si>
+  <si>
+    <t>Debiprasanna Patra</t>
+  </si>
+  <si>
+    <t>debiprasanna.patra@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-22343</t>
+  </si>
+  <si>
+    <t>Mayur Khairnar</t>
+  </si>
+  <si>
+    <t>mayur.khairnar@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-23223</t>
+  </si>
+  <si>
+    <t>Shubham Kumar Pachauri</t>
+  </si>
+  <si>
+    <t>shubham.pachauri@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-260216</t>
+  </si>
+  <si>
+    <t>Sailendra Biswal</t>
+  </si>
+  <si>
+    <t>sailendra.biswal@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-250356</t>
+  </si>
+  <si>
+    <t>Amulya Sachin Ambre</t>
+  </si>
+  <si>
+    <t>amulya.ambre@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Aarti Jaiswal</t>
+  </si>
+  <si>
+    <t>A-1870</t>
+  </si>
+  <si>
+    <t>bishnu.rath@apmosysuat1.com</t>
   </si>
 </sst>
 </file>
@@ -120,17 +384,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.55859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="17.15625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.62890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.1875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="30.0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.890625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.890625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.54296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.17578125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.21875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="19.328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="20.62109375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="20.34375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.109375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="30.0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="40.0" customWidth="true" bestFit="true"/>
   </cols>
@@ -167,6 +431,830 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27"/>
+      <c r="J27"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/EmployeeBillableData_6.xlsx
+++ b/EmployeeBillableData_6.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="101">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -243,6 +243,15 @@
   </si>
   <si>
     <t>saurav.bakshi@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>A-26202</t>
+  </si>
+  <si>
+    <t>test usera</t>
+  </si>
+  <si>
+    <t>test.usera@apmosys.com</t>
   </si>
   <si>
     <t>A-22358</t>
@@ -384,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.62890625" customWidth="true" bestFit="true"/>
@@ -1045,23 +1054,19 @@
       <c r="C21" t="s">
         <v>79</v>
       </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
+      <c r="D21"/>
+      <c r="E21"/>
       <c r="F21" t="s">
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="J21" t="s">
         <v>19</v>
@@ -1087,7 +1092,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1119,13 +1124,13 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
@@ -1151,7 +1156,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1183,7 +1188,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1215,7 +1220,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1229,10 +1234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
         <v>96</v>
-      </c>
-      <c r="B27" t="s">
-        <v>17</v>
       </c>
       <c r="C27" t="s">
         <v>97</v>
@@ -1247,13 +1252,45 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
         <v>26</v>
       </c>
-      <c r="H27" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27"/>
-      <c r="J27"/>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28"/>
+      <c r="J28"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
